--- a/programlar.xlsx
+++ b/programlar.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53F6EB7E-4775-4BFA-9FEF-75FA7ABE43E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="9a" sheetId="1" r:id="rId1"/>
